--- a/Metadata Anomali BPS Provinsi Sulawesi Tengah.xlsx
+++ b/Metadata Anomali BPS Provinsi Sulawesi Tengah.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="133">
   <si>
     <t>No</t>
   </si>
@@ -85,6 +85,41 @@
     <t>Jika r13b1=2 namun rasio dari r26b dan r26f lebih dari 50%</t>
   </si>
   <si>
+    <t>WITH numbered AS (
+    SELECT
+        level_2_code,
+        level_2_name,
+        level_3_code,
+        level_3_name,
+        level_4_code,
+        level_4_name,
+        level_5_code,
+        level_5_name,
+        level_6_code,
+        level_6_name,
+        nama_usaha,
+        nama_usaha_edit,
+        pengusaha_var_label,
+        no_bang_l,
+        no_usaha,
+        produk_sendiri_value,
+        total_pengeluaran,
+        biaya_produksi,
+        (biaya_produksi * 100.0 / NULLIF(total_pengeluaran, 0)) AS persentase_biaya_produksi,
+        assignment_id,
+        CONCAT('https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/', assignment_id) AS link_assignment,
+        ROW_NUMBER() OVER (ORDER BY assignment_id, no_usaha) AS rn
+    FROM tgr_fd68e454.se2026_nested
+    WHERE produk_sendiri_value = '2' AND (biaya_produksi * 100.0 / NULLIF(total_pengeluaran, 0)) &gt; 50
+)
+SELECT * FROM numbered
+WHERE rn BETWEEN 1 AND 1000
+ORDER BY rn</t>
+  </si>
+  <si>
+    <t>Ubah pada between 1 AND 1000 untuk mendapatkan nilai selanjutnya</t>
+  </si>
+  <si>
     <t>Keuntungan Usaha</t>
   </si>
   <si>
@@ -94,6 +129,37 @@
     <t>Selisih dari r27c dikurang r26f kurang dari nol</t>
   </si>
   <si>
+    <t>WITH numbered AS (
+    SELECT
+        level_2_code,
+        level_2_name,
+        level_3_code,
+        level_3_name,
+        level_4_code,
+        level_4_name,
+        level_5_code,
+        level_5_name,
+        level_6_code,
+        level_6_name,
+        nama_usaha,
+        nama_usaha_edit,
+        pengusaha_var_label,
+        no_bang_l,
+        no_usaha,
+        total_pendapatan,
+        total_pengeluaran,
+        total_pendapatan - total_pengeluaran AS keuntungan,
+        assignment_id,
+        CONCAT('https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/', assignment_id) AS link_assignment,
+        ROW_NUMBER() OVER (ORDER BY assignment_id, no_usaha) AS rn
+    FROM tgr_fd68e454.se2026_nested
+    WHERE total_pendapatan - total_pengeluaran &lt; 0
+)
+SELECT * FROM numbered
+WHERE rn BETWEEN 1 AND 1000
+ORDER BY rn</t>
+  </si>
+  <si>
     <t>Penyertaan Modal Korporasi</t>
   </si>
   <si>
@@ -103,6 +169,39 @@
     <t>R.11a diisi kode 13, namun pada rincian kepemilikan modal (R.29 atau R33), persentase kepemilikan modal korporasi publik (huruf c) atau korporasi non publik (huruf d) bernilai &gt;0</t>
   </si>
   <si>
+    <t>WITH numbered AS (
+    SELECT
+        level_2_code,
+        level_2_name,
+        level_3_code,
+        level_3_name,
+        level_4_code,
+        level_4_name,
+        level_5_code,
+        level_5_name,
+        level_6_code,
+        level_6_name,
+        nama_usaha,
+        nama_usaha_edit,
+        pengusaha_var_label,
+        no_bang_l,
+        no_usaha,
+        badan_usaha_value,
+        publik,
+        publik_didirikan,
+        non_publik,
+        nonpublik_didirikan
+        assignment_id,
+        CONCAT('https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/', assignment_id) AS link_assignment,
+        ROW_NUMBER() OVER (ORDER BY assignment_id, no_usaha) AS rn
+    FROM tgr_fd68e454.se2026_nested
+    WHERE badan_usaha_value = '13' AND (publik &gt; 0 OR publik_didirikan &gt; 0 OR non_publik &gt; 0 OR nonpublik_didirikan &gt; 0)
+)
+SELECT * FROM numbered
+WHERE rn BETWEEN 1 AND 1000
+ORDER BY rn</t>
+  </si>
+  <si>
     <t>Data Keuangan MBG</t>
   </si>
   <si>
@@ -112,9 +211,76 @@
     <t>R.22 diisi kode 1 (SPPG), namun pada rincian biaya produksi (R.26b atau R.30b) bernilai 0 atau 9999 atau pada rincian Nilai produksi/penjualan/pendapatan barang dan jasa (R.27a atau R31a) bernilai 0 atau 9999</t>
   </si>
   <si>
+    <t>WITH numbered AS (
+    SELECT
+        level_2_code,
+        level_2_name,
+        level_3_code,
+        level_3_name,
+        level_4_code,
+        level_4_name,
+        level_5_code,
+        level_5_name,
+        level_6_code,
+        level_6_name,
+        nama_usaha,
+        nama_usaha_edit,
+        no_bang_l,
+        no_usaha,
+        peran_mbg_value,
+        biaya_produksi,
+        biaya_produksi_bln,
+        nilai_pendapatan,
+        nilai_pendapatan_bln
+        assignment_id,
+        ROW_NUMBER() OVER (ORDER BY assignment_id, no_usaha) AS rn
+    FROM tgr_fd68e454.se2026_nested
+    WHERE peran_mbg_value = '2' AND (biaya_produksi IN (0, 9999) OR biaya_produksi_bln IN (0, 9999) OR nilai_pendapatan IN (0, 9999) OR nilai_pendapatan_bln IN (0, 9999))
+)
+SELECT * FROM numbered
+WHERE rn BETWEEN 1 AND 1000
+ORDER BY rn</t>
+  </si>
+  <si>
     <t>R.22 diisi kode 1 (SPPG), namun rasio total pendapatan (R.27c atau 31c) dengan total pengeluaran (R.26f atau R.33f) lebih dari 1.25 atau kurang dari 1</t>
   </si>
   <si>
+    <t>WITH numbered AS (
+    SELECT
+        level_2_code,
+        level_2_name,
+        level_3_code,
+        level_3_name,
+        level_4_code,
+        level_4_name,
+        level_5_code,
+        level_5_name,
+        level_6_code,
+        level_6_name,
+        nama_usaha,
+        nama_usaha_edit,
+        pengusaha_var_label,
+        no_bang_l,
+        no_usaha,
+        peran_mbg_value,
+        biaya_produksi,
+        biaya_produksi_bln,
+        nilai_pendapatan,
+        nilai_pendapatan_bln
+        assignment_id,
+        CONCAT('https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/', assignment_id) AS link_assignment,
+        ROW_NUMBER() OVER (ORDER BY assignment_id, no_usaha) AS rn
+    FROM tgr_fd68e454.se2026_nested
+    WHERE peran_mbg_value = '1' AND (biaya_produksi IN (0, 9999) OR biaya_produksi_bln IN (0, 9999) OR nilai_pendapatan IN (0, 9999) OR nilai_pendapatan_bln IN (0, 9999))
+)
+SELECT * FROM numbered
+WHERE rn BETWEEN 1 AND 1000
+ORDER BY rn</t>
+  </si>
+  <si>
+    <t>26f dan 30f</t>
+  </si>
+  <si>
     <t>R.22 diisi kode 1 (SPPG), namun rasio total pendapatan (R.27c atau 31c) dengan total pengeluaran (R.26f atau R.33f) lebih dari 1 dan kurang dari 1,25</t>
   </si>
   <si>
@@ -145,6 +311,9 @@
     <t>Jika r9a diisi usaha keliling, namun r28a (nilai aset tanah dan bangunan) bernilai &gt;0</t>
   </si>
   <si>
+    <t>tambahkan aset tanah dan bangunan bulanan 32. a</t>
+  </si>
+  <si>
     <t>Usaha Berbadan Hukum Ada Pekerja Keluarga</t>
   </si>
   <si>
@@ -278,13 +447,121 @@
   </si>
   <si>
     <t>"Jumlah Usaha Pertanian SE2026 memiliki nilai kurang lebih 20% dengan hasil ST2023 menurut SLS"</t>
+  </si>
+  <si>
+    <t>Rasio Keuntungan Usaha (pendapatan - pengeluaran) melebihi 80%</t>
+  </si>
+  <si>
+    <t>(Pendapatan_total - Pengeluaran_total)/Pengeluaran &gt; 80%</t>
+  </si>
+  <si>
+    <t>Rasio Biaya Produksi Pada Kategori G lebih dari 50%</t>
+  </si>
+  <si>
+    <t>Jika KBLI berkategori G , Nilai (biaya produksi - total pengeluaran)/total pengeluaran &gt; 50%</t>
+  </si>
+  <si>
+    <t>Kategori pertanian namun beroprasi di kawasan ekonomi</t>
+  </si>
+  <si>
+    <t>Jika KBLI berkode A, namun tempat beroprasi terisi selain diluar kawasan  (kode 10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kategori pertanian, namun kepemilikan modal selain perorangan </t>
+  </si>
+  <si>
+    <t>KBLI berkode A, status badan usaha lainnya, namun kepemilikan modal ada terisi selain perorangan</t>
+  </si>
+  <si>
+    <t>Kawasan beroprasi di stasiun atau rest area</t>
+  </si>
+  <si>
+    <t>Kawasan beroprasi berkode 3 atau 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kawasan beroprasi di KEK </t>
+  </si>
+  <si>
+    <t>Kode kabupaten/kota selain 7271 namun ada kawasan beroprasi berkode 1</t>
+  </si>
+  <si>
+    <t>Kawasan beroprasi selain KI</t>
+  </si>
+  <si>
+    <t>Kode kabupaten/kota selain 7203 dan 7212,  namun ada kawasan beroprasi berkode 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produksi dan distribusi menggunakan internet tidak sesuai KBLI </t>
+  </si>
+  <si>
+    <t>Rincian 16/12 b2 dan atau b3 berkode Ya namun kbli selain J,K,L,Q, dan T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ada aset namun tidak ada lahan yang dikuasai </t>
+  </si>
+  <si>
+    <t>Rincian 28.a terisi namun 28.d terisi 0</t>
+  </si>
+  <si>
+    <t>Hubungan Pendapatan usaha pada sosek dan usaha pada L</t>
+  </si>
+  <si>
+    <t>Rincian (27d - 26f)/12 &lt;  rincian 18.b1 (sosek)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missing Value PLN </t>
+  </si>
+  <si>
+    <t>Meteran Berkode 9999</t>
+  </si>
+  <si>
+    <t>Hidup ditopang orang lain namun tidak ada keluhan kesehatan, disabilitas, dan catatan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rincian 18.a dan Rincian 18.b bernilai tidak , tidak ada pilihan ya pada keluhan kesehatan dan disabilitas, serta tidak ada catatan </t>
+  </si>
+  <si>
+    <t>Konsistensi atap lantai dan dinding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6a &gt; 5, maka 8a tidak boleh 1, jika 7a selain 1 maka 8a tidak boleh 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sumber air lainnya </t>
+  </si>
+  <si>
+    <t>Rincian 12 berkode 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konsistensi meteran </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jika rincian 14 b &gt; 3, maka 15 a &lt; 50 ribu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cak data input otomatis GC PBI </t>
+  </si>
+  <si>
+    <t>Cek 17d = 2 &amp;&amp; 17h = 2</t>
+  </si>
+  <si>
+    <t>Cek status pemilik usaha</t>
+  </si>
+  <si>
+    <t>Jika R.33a atau 29a = 100 &amp;&amp; R.24b2 = 0</t>
+  </si>
+  <si>
+    <t>Industri Kopra tanpa Kebun Kelapa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cek apabila ada usaha industri kopra namun tidak ada usaha perkebunan kelapa pada nik pemilik usaha yang sama </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="11">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -326,17 +603,7 @@
     </font>
     <font>
       <sz val="13.0"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="13.0"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="13.0"/>
-      <color rgb="FF2892C6"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -371,7 +638,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -394,10 +661,10 @@
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -408,19 +675,13 @@
     <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -862,15 +1123,19 @@
       <c r="F6" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="8"/>
+      <c r="G6" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="2">
         <v>6.0</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>9</v>
@@ -879,12 +1144,14 @@
         <v>21</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="6"/>
+        <v>28</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="H7" s="8"/>
     </row>
     <row r="8" ht="22.5" customHeight="1">
@@ -892,7 +1159,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>9</v>
@@ -901,12 +1168,14 @@
         <v>21</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" s="6"/>
+        <v>32</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="H8" s="8"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
@@ -914,7 +1183,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>9</v>
@@ -923,12 +1192,14 @@
         <v>21</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="6"/>
+        <v>36</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="H9" s="8"/>
     </row>
     <row r="10" ht="22.5" customHeight="1">
@@ -936,7 +1207,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>9</v>
@@ -945,20 +1216,24 @@
         <v>21</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="8"/>
+        <v>38</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="2">
         <v>10.0</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>30</v>
+      <c r="B11" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>9</v>
@@ -967,10 +1242,10 @@
         <v>21</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="8"/>
@@ -979,8 +1254,8 @@
       <c r="A12" s="2">
         <v>11.0</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>35</v>
+      <c r="B12" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>9</v>
@@ -989,10 +1264,10 @@
         <v>21</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="8"/>
@@ -1001,8 +1276,8 @@
       <c r="A13" s="2">
         <v>12.0</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>38</v>
+      <c r="B13" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>9</v>
@@ -1011,10 +1286,10 @@
         <v>21</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="8"/>
@@ -1023,8 +1298,8 @@
       <c r="A14" s="2">
         <v>13.0</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>41</v>
+      <c r="B14" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>9</v>
@@ -1033,20 +1308,22 @@
         <v>21</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G14" s="6"/>
-      <c r="H14" s="8"/>
+      <c r="H14" s="7" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="2">
         <v>14.0</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>44</v>
+      <c r="B15" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>9</v>
@@ -1055,10 +1332,10 @@
         <v>21</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="8"/>
@@ -1067,8 +1344,8 @@
       <c r="A16" s="2">
         <v>15.0</v>
       </c>
-      <c r="B16" s="13" t="s">
-        <v>47</v>
+      <c r="B16" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>9</v>
@@ -1077,10 +1354,10 @@
         <v>21</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="8"/>
@@ -1089,8 +1366,8 @@
       <c r="A17" s="2">
         <v>16.0</v>
       </c>
-      <c r="B17" s="13" t="s">
-        <v>50</v>
+      <c r="B17" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>9</v>
@@ -1099,10 +1376,10 @@
         <v>21</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="8"/>
@@ -1111,8 +1388,8 @@
       <c r="A18" s="2">
         <v>17.0</v>
       </c>
-      <c r="B18" s="13" t="s">
-        <v>53</v>
+      <c r="B18" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>9</v>
@@ -1121,10 +1398,10 @@
         <v>21</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="8"/>
@@ -1133,8 +1410,8 @@
       <c r="A19" s="2">
         <v>18.0</v>
       </c>
-      <c r="B19" s="14" t="s">
-        <v>56</v>
+      <c r="B19" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>9</v>
@@ -1143,7 +1420,7 @@
         <v>21</v>
       </c>
       <c r="E19" s="13"/>
-      <c r="F19" s="15"/>
+      <c r="F19" s="14"/>
       <c r="G19" s="6"/>
       <c r="H19" s="8"/>
     </row>
@@ -1151,8 +1428,8 @@
       <c r="A20" s="2">
         <v>19.0</v>
       </c>
-      <c r="B20" s="14" t="s">
-        <v>57</v>
+      <c r="B20" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>9</v>
@@ -1161,7 +1438,7 @@
         <v>21</v>
       </c>
       <c r="E20" s="13"/>
-      <c r="F20" s="15"/>
+      <c r="F20" s="14"/>
       <c r="G20" s="6"/>
       <c r="H20" s="8"/>
     </row>
@@ -1169,8 +1446,8 @@
       <c r="A21" s="2">
         <v>20.0</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>58</v>
+      <c r="B21" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>9</v>
@@ -1179,7 +1456,7 @@
         <v>21</v>
       </c>
       <c r="E21" s="13"/>
-      <c r="F21" s="15"/>
+      <c r="F21" s="14"/>
       <c r="G21" s="6"/>
       <c r="H21" s="8"/>
     </row>
@@ -1187,8 +1464,8 @@
       <c r="A22" s="2">
         <v>21.0</v>
       </c>
-      <c r="B22" s="13" t="s">
-        <v>59</v>
+      <c r="B22" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>9</v>
@@ -1197,7 +1474,7 @@
         <v>21</v>
       </c>
       <c r="E22" s="13"/>
-      <c r="F22" s="15"/>
+      <c r="F22" s="14"/>
       <c r="G22" s="6"/>
       <c r="H22" s="8"/>
     </row>
@@ -1205,8 +1482,8 @@
       <c r="A23" s="2">
         <v>22.0</v>
       </c>
-      <c r="B23" s="12" t="s">
-        <v>60</v>
+      <c r="B23" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>9</v>
@@ -1215,10 +1492,10 @@
         <v>21</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="8"/>
@@ -1227,8 +1504,8 @@
       <c r="A24" s="2">
         <v>23.0</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>62</v>
+      <c r="B24" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>9</v>
@@ -1237,10 +1514,10 @@
         <v>21</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="8"/>
@@ -1249,8 +1526,8 @@
       <c r="A25" s="2">
         <v>24.0</v>
       </c>
-      <c r="B25" s="13" t="s">
-        <v>65</v>
+      <c r="B25" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>9</v>
@@ -1259,10 +1536,10 @@
         <v>21</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="8"/>
@@ -1271,8 +1548,8 @@
       <c r="A26" s="2">
         <v>25.0</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>67</v>
+      <c r="B26" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>9</v>
@@ -1281,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="6"/>
@@ -1291,8 +1568,8 @@
       <c r="A27" s="2">
         <v>26.0</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>69</v>
+      <c r="B27" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>9</v>
@@ -1301,7 +1578,7 @@
         <v>21</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="6"/>
@@ -1311,8 +1588,8 @@
       <c r="A28" s="2">
         <v>27.0</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>71</v>
+      <c r="B28" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>9</v>
@@ -1321,7 +1598,7 @@
         <v>21</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="6"/>
@@ -1331,8 +1608,8 @@
       <c r="A29" s="2">
         <v>28.0</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>73</v>
+      <c r="B29" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>18</v>
@@ -1341,7 +1618,7 @@
         <v>21</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="6"/>
@@ -1351,8 +1628,8 @@
       <c r="A30" s="2">
         <v>29.0</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>75</v>
+      <c r="B30" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>18</v>
@@ -1361,7 +1638,7 @@
         <v>21</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="6"/>
@@ -1371,8 +1648,8 @@
       <c r="A31" s="2">
         <v>30.0</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>77</v>
+      <c r="B31" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>18</v>
@@ -1381,7 +1658,7 @@
         <v>21</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="6"/>
@@ -1391,8 +1668,8 @@
       <c r="A32" s="2">
         <v>31.0</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>79</v>
+      <c r="B32" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>18</v>
@@ -1401,7 +1678,7 @@
         <v>21</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="6"/>
@@ -1411,8 +1688,8 @@
       <c r="A33" s="2">
         <v>32.0</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>81</v>
+      <c r="B33" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>18</v>
@@ -1421,7 +1698,7 @@
         <v>21</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="6"/>
@@ -1431,8 +1708,8 @@
       <c r="A34" s="2">
         <v>33.0</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>83</v>
+      <c r="B34" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>18</v>
@@ -1441,7 +1718,7 @@
         <v>21</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="6"/>
@@ -1451,8 +1728,8 @@
       <c r="A35" s="2">
         <v>34.0</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>84</v>
+      <c r="B35" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>18</v>
@@ -1461,7 +1738,7 @@
         <v>21</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="6"/>
@@ -1471,938 +1748,1118 @@
       <c r="A36" s="2">
         <v>35.0</v>
       </c>
-      <c r="B36" s="16" t="s">
-        <v>86</v>
+      <c r="B36" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>88</v>
+        <v>95</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="8"/>
     </row>
     <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="6"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="6"/>
+      <c r="A37" s="2">
+        <v>36.0</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>98</v>
+      </c>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="8"/>
     </row>
     <row r="38" ht="22.5" customHeight="1">
-      <c r="A38" s="6"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="6"/>
+      <c r="A38" s="2">
+        <v>37.0</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>100</v>
+      </c>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="8"/>
     </row>
     <row r="39" ht="22.5" customHeight="1">
-      <c r="A39" s="6"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="6"/>
+      <c r="A39" s="2">
+        <v>38.0</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>102</v>
+      </c>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
       <c r="H39" s="8"/>
     </row>
     <row r="40" ht="22.5" customHeight="1">
-      <c r="A40" s="6"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="6"/>
+      <c r="A40" s="2">
+        <v>39.0</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>104</v>
+      </c>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
       <c r="H40" s="8"/>
     </row>
     <row r="41" ht="22.5" customHeight="1">
-      <c r="A41" s="6"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="6"/>
+      <c r="A41" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>106</v>
+      </c>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
       <c r="H41" s="8"/>
     </row>
     <row r="42" ht="22.5" customHeight="1">
-      <c r="A42" s="6"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="6"/>
+      <c r="A42" s="2">
+        <v>41.0</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>108</v>
+      </c>
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
       <c r="H42" s="8"/>
     </row>
     <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="6"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="6"/>
+      <c r="A43" s="2">
+        <v>42.0</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>110</v>
+      </c>
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
       <c r="H43" s="8"/>
     </row>
     <row r="44" ht="22.5" customHeight="1">
-      <c r="A44" s="6"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="6"/>
+      <c r="A44" s="2">
+        <v>43.0</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>112</v>
+      </c>
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
       <c r="H44" s="8"/>
     </row>
     <row r="45" ht="22.5" customHeight="1">
-      <c r="A45" s="6"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="6"/>
+      <c r="A45" s="2">
+        <v>44.0</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>114</v>
+      </c>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="8"/>
     </row>
     <row r="46" ht="22.5" customHeight="1">
-      <c r="A46" s="6"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="6"/>
+      <c r="A46" s="2">
+        <v>45.0</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>116</v>
+      </c>
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
       <c r="H46" s="8"/>
     </row>
     <row r="47" ht="22.5" customHeight="1">
-      <c r="A47" s="6"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="6"/>
+      <c r="A47" s="2">
+        <v>46.0</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="8"/>
     </row>
     <row r="48" ht="22.5" customHeight="1">
-      <c r="A48" s="6"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="6"/>
+      <c r="A48" s="2">
+        <v>47.0</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>120</v>
+      </c>
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
       <c r="H48" s="8"/>
     </row>
     <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" s="6"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
+      <c r="A49" s="2">
+        <v>48.0</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F49" s="2"/>
       <c r="G49" s="6"/>
       <c r="H49" s="8"/>
     </row>
     <row r="50" ht="22.5" customHeight="1">
-      <c r="A50" s="6"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="18"/>
-      <c r="E50" s="6"/>
+      <c r="A50" s="2">
+        <v>49.0</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>124</v>
+      </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
       <c r="H50" s="8"/>
     </row>
     <row r="51" ht="22.5" customHeight="1">
-      <c r="A51" s="6"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="6"/>
+      <c r="A51" s="2">
+        <v>50.0</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>126</v>
+      </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
       <c r="H51" s="8"/>
     </row>
     <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="6"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="18"/>
-      <c r="D52" s="18"/>
-      <c r="E52" s="6"/>
+      <c r="A52" s="2">
+        <v>51.0</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
       <c r="H52" s="8"/>
     </row>
     <row r="53" ht="22.5" customHeight="1">
-      <c r="A53" s="6"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="6"/>
+      <c r="A53" s="2">
+        <v>52.0</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>130</v>
+      </c>
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
       <c r="H53" s="8"/>
     </row>
     <row r="54" ht="22.5" customHeight="1">
-      <c r="A54" s="6"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="18"/>
-      <c r="D54" s="18"/>
-      <c r="E54" s="6"/>
+      <c r="A54" s="2">
+        <v>53.0</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>132</v>
+      </c>
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
       <c r="H54" s="8"/>
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="6"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="6"/>
+      <c r="B55" s="15"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="15"/>
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
       <c r="H55" s="8"/>
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="6"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="18"/>
-      <c r="E56" s="6"/>
+      <c r="B56" s="15"/>
+      <c r="C56" s="16"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="15"/>
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
       <c r="H56" s="8"/>
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="6"/>
-      <c r="B57" s="17"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="18"/>
-      <c r="E57" s="6"/>
+      <c r="B57" s="15"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="15"/>
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
       <c r="H57" s="8"/>
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="6"/>
-      <c r="B58" s="17"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="18"/>
-      <c r="E58" s="6"/>
+      <c r="B58" s="15"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="15"/>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
       <c r="H58" s="8"/>
     </row>
     <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="6"/>
-      <c r="B59" s="17"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="18"/>
-      <c r="E59" s="6"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="15"/>
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
       <c r="H59" s="8"/>
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="6"/>
-      <c r="B60" s="17"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="18"/>
-      <c r="E60" s="6"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="15"/>
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
       <c r="H60" s="8"/>
     </row>
     <row r="61" ht="22.5" customHeight="1">
       <c r="A61" s="6"/>
-      <c r="B61" s="17"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="18"/>
-      <c r="E61" s="6"/>
+      <c r="B61" s="15"/>
+      <c r="C61" s="16"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="15"/>
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
       <c r="H61" s="8"/>
     </row>
     <row r="62" ht="22.5" customHeight="1">
       <c r="A62" s="6"/>
-      <c r="B62" s="17"/>
-      <c r="C62" s="18"/>
-      <c r="D62" s="18"/>
-      <c r="E62" s="6"/>
+      <c r="B62" s="15"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="15"/>
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
       <c r="H62" s="8"/>
     </row>
     <row r="63" ht="22.5" customHeight="1">
       <c r="A63" s="6"/>
-      <c r="B63" s="17"/>
-      <c r="C63" s="18"/>
-      <c r="D63" s="18"/>
-      <c r="E63" s="6"/>
+      <c r="B63" s="15"/>
+      <c r="C63" s="16"/>
+      <c r="D63" s="16"/>
+      <c r="E63" s="15"/>
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
       <c r="H63" s="8"/>
     </row>
     <row r="64" ht="22.5" customHeight="1">
       <c r="A64" s="6"/>
-      <c r="B64" s="17"/>
-      <c r="C64" s="18"/>
-      <c r="D64" s="18"/>
-      <c r="E64" s="6"/>
+      <c r="B64" s="15"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="15"/>
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
       <c r="H64" s="8"/>
     </row>
     <row r="65" ht="22.5" customHeight="1">
       <c r="A65" s="6"/>
-      <c r="B65" s="17"/>
-      <c r="C65" s="18"/>
-      <c r="D65" s="18"/>
-      <c r="E65" s="6"/>
+      <c r="B65" s="15"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="15"/>
       <c r="F65" s="6"/>
       <c r="G65" s="6"/>
       <c r="H65" s="8"/>
     </row>
     <row r="66" ht="22.5" customHeight="1">
       <c r="A66" s="6"/>
-      <c r="B66" s="17"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="18"/>
-      <c r="E66" s="6"/>
+      <c r="B66" s="15"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="15"/>
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
       <c r="H66" s="8"/>
     </row>
     <row r="67" ht="22.5" customHeight="1">
       <c r="A67" s="6"/>
-      <c r="B67" s="17"/>
-      <c r="C67" s="18"/>
-      <c r="D67" s="18"/>
-      <c r="E67" s="6"/>
+      <c r="B67" s="15"/>
+      <c r="C67" s="16"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="15"/>
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
       <c r="H67" s="8"/>
     </row>
     <row r="68" ht="22.5" customHeight="1">
       <c r="A68" s="6"/>
-      <c r="B68" s="17"/>
-      <c r="C68" s="18"/>
-      <c r="D68" s="18"/>
-      <c r="E68" s="6"/>
+      <c r="B68" s="15"/>
+      <c r="C68" s="16"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="15"/>
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
       <c r="H68" s="8"/>
     </row>
     <row r="69" ht="22.5" customHeight="1">
       <c r="A69" s="6"/>
-      <c r="B69" s="17"/>
-      <c r="C69" s="18"/>
-      <c r="D69" s="18"/>
-      <c r="E69" s="6"/>
+      <c r="B69" s="15"/>
+      <c r="C69" s="16"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="15"/>
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
       <c r="H69" s="8"/>
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="6"/>
-      <c r="B70" s="17"/>
-      <c r="C70" s="18"/>
-      <c r="D70" s="18"/>
-      <c r="E70" s="6"/>
+      <c r="B70" s="15"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="15"/>
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
       <c r="H70" s="8"/>
     </row>
     <row r="71" ht="22.5" customHeight="1">
       <c r="A71" s="6"/>
-      <c r="B71" s="17"/>
-      <c r="C71" s="18"/>
-      <c r="D71" s="18"/>
-      <c r="E71" s="6"/>
+      <c r="B71" s="15"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="15"/>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
       <c r="H71" s="8"/>
     </row>
     <row r="72" ht="22.5" customHeight="1">
       <c r="A72" s="6"/>
-      <c r="B72" s="17"/>
-      <c r="C72" s="18"/>
-      <c r="D72" s="18"/>
-      <c r="E72" s="6"/>
+      <c r="B72" s="15"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="15"/>
       <c r="F72" s="6"/>
       <c r="G72" s="6"/>
       <c r="H72" s="8"/>
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="6"/>
-      <c r="B73" s="17"/>
-      <c r="C73" s="18"/>
-      <c r="D73" s="18"/>
-      <c r="E73" s="6"/>
+      <c r="B73" s="15"/>
+      <c r="C73" s="16"/>
+      <c r="D73" s="16"/>
+      <c r="E73" s="15"/>
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
       <c r="H73" s="8"/>
     </row>
     <row r="74" ht="22.5" customHeight="1">
       <c r="A74" s="6"/>
-      <c r="B74" s="17"/>
-      <c r="C74" s="18"/>
-      <c r="D74" s="18"/>
-      <c r="E74" s="6"/>
+      <c r="B74" s="15"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="15"/>
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
       <c r="H74" s="8"/>
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="6"/>
-      <c r="B75" s="17"/>
-      <c r="C75" s="18"/>
-      <c r="D75" s="18"/>
-      <c r="E75" s="6"/>
+      <c r="B75" s="15"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="15"/>
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
       <c r="H75" s="8"/>
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="6"/>
-      <c r="B76" s="17"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="18"/>
-      <c r="E76" s="6"/>
+      <c r="B76" s="15"/>
+      <c r="C76" s="16"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="15"/>
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
       <c r="H76" s="8"/>
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="6"/>
-      <c r="B77" s="17"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="6"/>
+      <c r="B77" s="15"/>
+      <c r="C77" s="16"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="15"/>
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
       <c r="H77" s="8"/>
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="6"/>
-      <c r="B78" s="17"/>
-      <c r="C78" s="18"/>
-      <c r="D78" s="18"/>
-      <c r="E78" s="6"/>
+      <c r="B78" s="15"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="15"/>
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
       <c r="H78" s="8"/>
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="6"/>
-      <c r="B79" s="17"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="18"/>
-      <c r="E79" s="6"/>
+      <c r="B79" s="15"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="15"/>
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
       <c r="H79" s="8"/>
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="6"/>
-      <c r="B80" s="17"/>
-      <c r="C80" s="18"/>
-      <c r="D80" s="18"/>
-      <c r="E80" s="6"/>
+      <c r="B80" s="15"/>
+      <c r="C80" s="16"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="15"/>
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
       <c r="H80" s="8"/>
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="6"/>
-      <c r="B81" s="17"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="18"/>
-      <c r="E81" s="6"/>
+      <c r="B81" s="15"/>
+      <c r="C81" s="16"/>
+      <c r="D81" s="16"/>
+      <c r="E81" s="15"/>
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
       <c r="H81" s="8"/>
     </row>
     <row r="82" ht="22.5" customHeight="1">
       <c r="A82" s="6"/>
-      <c r="B82" s="17"/>
-      <c r="C82" s="18"/>
-      <c r="D82" s="18"/>
-      <c r="E82" s="6"/>
+      <c r="B82" s="15"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="16"/>
+      <c r="E82" s="15"/>
       <c r="F82" s="6"/>
       <c r="G82" s="6"/>
       <c r="H82" s="8"/>
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="6"/>
-      <c r="B83" s="17"/>
-      <c r="C83" s="18"/>
-      <c r="D83" s="18"/>
-      <c r="E83" s="6"/>
+      <c r="B83" s="15"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="15"/>
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
       <c r="H83" s="8"/>
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="6"/>
-      <c r="B84" s="17"/>
-      <c r="C84" s="18"/>
-      <c r="D84" s="18"/>
-      <c r="E84" s="6"/>
+      <c r="B84" s="15"/>
+      <c r="C84" s="16"/>
+      <c r="D84" s="16"/>
+      <c r="E84" s="15"/>
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
       <c r="H84" s="8"/>
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="6"/>
-      <c r="B85" s="17"/>
-      <c r="C85" s="18"/>
-      <c r="D85" s="18"/>
-      <c r="E85" s="6"/>
+      <c r="B85" s="15"/>
+      <c r="C85" s="16"/>
+      <c r="D85" s="16"/>
+      <c r="E85" s="15"/>
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
       <c r="H85" s="8"/>
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="6"/>
-      <c r="B86" s="17"/>
-      <c r="C86" s="18"/>
-      <c r="D86" s="18"/>
-      <c r="E86" s="6"/>
+      <c r="B86" s="15"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="16"/>
+      <c r="E86" s="15"/>
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
       <c r="H86" s="8"/>
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="6"/>
-      <c r="B87" s="17"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="18"/>
-      <c r="E87" s="6"/>
+      <c r="B87" s="15"/>
+      <c r="C87" s="16"/>
+      <c r="D87" s="16"/>
+      <c r="E87" s="15"/>
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
       <c r="H87" s="8"/>
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="6"/>
-      <c r="B88" s="17"/>
-      <c r="C88" s="18"/>
-      <c r="D88" s="18"/>
-      <c r="E88" s="6"/>
+      <c r="B88" s="15"/>
+      <c r="C88" s="16"/>
+      <c r="D88" s="16"/>
+      <c r="E88" s="15"/>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
       <c r="H88" s="8"/>
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="6"/>
-      <c r="B89" s="17"/>
-      <c r="C89" s="18"/>
-      <c r="D89" s="18"/>
-      <c r="E89" s="6"/>
+      <c r="B89" s="15"/>
+      <c r="C89" s="16"/>
+      <c r="D89" s="16"/>
+      <c r="E89" s="15"/>
       <c r="F89" s="6"/>
       <c r="G89" s="6"/>
       <c r="H89" s="8"/>
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="6"/>
-      <c r="B90" s="17"/>
-      <c r="C90" s="18"/>
-      <c r="D90" s="18"/>
-      <c r="E90" s="6"/>
+      <c r="B90" s="15"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="16"/>
+      <c r="E90" s="15"/>
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
       <c r="H90" s="8"/>
     </row>
     <row r="91" ht="22.5" customHeight="1">
       <c r="A91" s="6"/>
-      <c r="B91" s="17"/>
-      <c r="C91" s="18"/>
-      <c r="D91" s="18"/>
-      <c r="E91" s="6"/>
+      <c r="B91" s="15"/>
+      <c r="C91" s="16"/>
+      <c r="D91" s="16"/>
+      <c r="E91" s="15"/>
       <c r="F91" s="6"/>
       <c r="G91" s="6"/>
       <c r="H91" s="8"/>
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="6"/>
-      <c r="B92" s="17"/>
-      <c r="C92" s="18"/>
-      <c r="D92" s="18"/>
-      <c r="E92" s="6"/>
+      <c r="B92" s="15"/>
+      <c r="C92" s="16"/>
+      <c r="D92" s="16"/>
+      <c r="E92" s="15"/>
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
       <c r="H92" s="8"/>
     </row>
     <row r="93" ht="22.5" customHeight="1">
       <c r="A93" s="6"/>
-      <c r="B93" s="17"/>
-      <c r="C93" s="18"/>
-      <c r="D93" s="18"/>
-      <c r="E93" s="6"/>
+      <c r="B93" s="15"/>
+      <c r="C93" s="16"/>
+      <c r="D93" s="16"/>
+      <c r="E93" s="15"/>
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
       <c r="H93" s="8"/>
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="6"/>
-      <c r="B94" s="17"/>
-      <c r="C94" s="18"/>
-      <c r="D94" s="18"/>
-      <c r="E94" s="6"/>
+      <c r="B94" s="15"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="16"/>
+      <c r="E94" s="15"/>
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
       <c r="H94" s="8"/>
     </row>
     <row r="95" ht="22.5" customHeight="1">
       <c r="A95" s="6"/>
-      <c r="B95" s="17"/>
-      <c r="C95" s="18"/>
-      <c r="D95" s="18"/>
-      <c r="E95" s="6"/>
+      <c r="B95" s="15"/>
+      <c r="C95" s="16"/>
+      <c r="D95" s="16"/>
+      <c r="E95" s="15"/>
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
       <c r="H95" s="8"/>
     </row>
     <row r="96" ht="22.5" customHeight="1">
       <c r="A96" s="6"/>
-      <c r="B96" s="17"/>
-      <c r="C96" s="18"/>
-      <c r="D96" s="18"/>
-      <c r="E96" s="6"/>
+      <c r="B96" s="15"/>
+      <c r="C96" s="16"/>
+      <c r="D96" s="16"/>
+      <c r="E96" s="15"/>
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
       <c r="H96" s="8"/>
     </row>
     <row r="97" ht="22.5" customHeight="1">
       <c r="A97" s="6"/>
-      <c r="B97" s="17"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="18"/>
-      <c r="E97" s="6"/>
+      <c r="B97" s="15"/>
+      <c r="C97" s="16"/>
+      <c r="D97" s="16"/>
+      <c r="E97" s="15"/>
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
       <c r="H97" s="8"/>
     </row>
     <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="6"/>
-      <c r="B98" s="17"/>
-      <c r="C98" s="18"/>
-      <c r="D98" s="18"/>
-      <c r="E98" s="6"/>
+      <c r="B98" s="15"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="16"/>
+      <c r="E98" s="15"/>
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
       <c r="H98" s="8"/>
     </row>
     <row r="99" ht="22.5" customHeight="1">
       <c r="A99" s="6"/>
-      <c r="B99" s="17"/>
-      <c r="C99" s="18"/>
-      <c r="D99" s="18"/>
-      <c r="E99" s="6"/>
+      <c r="B99" s="15"/>
+      <c r="C99" s="16"/>
+      <c r="D99" s="16"/>
+      <c r="E99" s="15"/>
       <c r="F99" s="6"/>
       <c r="G99" s="6"/>
       <c r="H99" s="8"/>
     </row>
     <row r="100" ht="22.5" customHeight="1">
       <c r="A100" s="6"/>
-      <c r="B100" s="17"/>
-      <c r="C100" s="18"/>
-      <c r="D100" s="18"/>
-      <c r="E100" s="6"/>
+      <c r="B100" s="15"/>
+      <c r="C100" s="16"/>
+      <c r="D100" s="16"/>
+      <c r="E100" s="15"/>
       <c r="F100" s="6"/>
       <c r="G100" s="6"/>
       <c r="H100" s="8"/>
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="6"/>
-      <c r="B101" s="17"/>
-      <c r="C101" s="18"/>
-      <c r="D101" s="18"/>
-      <c r="E101" s="6"/>
+      <c r="B101" s="15"/>
+      <c r="C101" s="16"/>
+      <c r="D101" s="16"/>
+      <c r="E101" s="15"/>
       <c r="F101" s="6"/>
       <c r="G101" s="6"/>
       <c r="H101" s="8"/>
     </row>
     <row r="102" ht="22.5" customHeight="1">
       <c r="A102" s="6"/>
-      <c r="B102" s="17"/>
-      <c r="C102" s="18"/>
-      <c r="D102" s="18"/>
-      <c r="E102" s="6"/>
+      <c r="B102" s="15"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="15"/>
       <c r="F102" s="6"/>
       <c r="G102" s="6"/>
       <c r="H102" s="8"/>
     </row>
     <row r="103" ht="22.5" customHeight="1">
       <c r="A103" s="6"/>
-      <c r="B103" s="17"/>
-      <c r="C103" s="18"/>
-      <c r="D103" s="18"/>
-      <c r="E103" s="6"/>
+      <c r="B103" s="15"/>
+      <c r="C103" s="16"/>
+      <c r="D103" s="16"/>
+      <c r="E103" s="15"/>
       <c r="F103" s="6"/>
       <c r="G103" s="6"/>
       <c r="H103" s="8"/>
     </row>
     <row r="104" ht="22.5" customHeight="1">
       <c r="A104" s="6"/>
-      <c r="B104" s="17"/>
-      <c r="C104" s="18"/>
-      <c r="D104" s="18"/>
-      <c r="E104" s="6"/>
+      <c r="B104" s="15"/>
+      <c r="C104" s="16"/>
+      <c r="D104" s="16"/>
+      <c r="E104" s="15"/>
       <c r="F104" s="6"/>
       <c r="G104" s="6"/>
       <c r="H104" s="8"/>
     </row>
     <row r="105" ht="22.5" customHeight="1">
       <c r="A105" s="6"/>
-      <c r="B105" s="17"/>
-      <c r="C105" s="18"/>
-      <c r="D105" s="18"/>
-      <c r="E105" s="6"/>
+      <c r="B105" s="15"/>
+      <c r="C105" s="16"/>
+      <c r="D105" s="16"/>
+      <c r="E105" s="15"/>
       <c r="F105" s="6"/>
       <c r="G105" s="6"/>
       <c r="H105" s="8"/>
     </row>
     <row r="106" ht="22.5" customHeight="1">
       <c r="A106" s="6"/>
-      <c r="B106" s="17"/>
-      <c r="C106" s="18"/>
-      <c r="D106" s="18"/>
-      <c r="E106" s="6"/>
+      <c r="B106" s="15"/>
+      <c r="C106" s="16"/>
+      <c r="D106" s="16"/>
+      <c r="E106" s="15"/>
       <c r="F106" s="6"/>
       <c r="G106" s="6"/>
       <c r="H106" s="8"/>
     </row>
     <row r="107" ht="22.5" customHeight="1">
       <c r="A107" s="6"/>
-      <c r="B107" s="17"/>
-      <c r="C107" s="18"/>
-      <c r="D107" s="18"/>
-      <c r="E107" s="6"/>
+      <c r="B107" s="15"/>
+      <c r="C107" s="16"/>
+      <c r="D107" s="16"/>
+      <c r="E107" s="15"/>
       <c r="F107" s="6"/>
       <c r="G107" s="6"/>
       <c r="H107" s="8"/>
     </row>
     <row r="108" ht="22.5" customHeight="1">
       <c r="A108" s="6"/>
-      <c r="B108" s="17"/>
-      <c r="C108" s="18"/>
-      <c r="D108" s="18"/>
-      <c r="E108" s="6"/>
+      <c r="B108" s="15"/>
+      <c r="C108" s="16"/>
+      <c r="D108" s="16"/>
+      <c r="E108" s="15"/>
       <c r="F108" s="6"/>
       <c r="G108" s="6"/>
       <c r="H108" s="8"/>
     </row>
     <row r="109" ht="22.5" customHeight="1">
       <c r="A109" s="6"/>
-      <c r="B109" s="17"/>
-      <c r="C109" s="18"/>
-      <c r="D109" s="18"/>
-      <c r="E109" s="6"/>
+      <c r="B109" s="15"/>
+      <c r="C109" s="16"/>
+      <c r="D109" s="16"/>
+      <c r="E109" s="15"/>
       <c r="F109" s="6"/>
       <c r="G109" s="6"/>
       <c r="H109" s="8"/>
     </row>
     <row r="110" ht="22.5" customHeight="1">
       <c r="A110" s="6"/>
-      <c r="B110" s="17"/>
-      <c r="C110" s="18"/>
-      <c r="D110" s="18"/>
-      <c r="E110" s="6"/>
+      <c r="B110" s="15"/>
+      <c r="C110" s="16"/>
+      <c r="D110" s="16"/>
+      <c r="E110" s="15"/>
       <c r="F110" s="6"/>
       <c r="G110" s="6"/>
       <c r="H110" s="8"/>
     </row>
     <row r="111" ht="22.5" customHeight="1">
       <c r="A111" s="6"/>
-      <c r="B111" s="17"/>
-      <c r="C111" s="18"/>
-      <c r="D111" s="18"/>
-      <c r="E111" s="6"/>
+      <c r="B111" s="15"/>
+      <c r="C111" s="16"/>
+      <c r="D111" s="16"/>
+      <c r="E111" s="15"/>
       <c r="F111" s="6"/>
       <c r="G111" s="6"/>
       <c r="H111" s="8"/>
     </row>
     <row r="112" ht="22.5" customHeight="1">
       <c r="A112" s="6"/>
-      <c r="B112" s="17"/>
-      <c r="C112" s="18"/>
-      <c r="D112" s="18"/>
-      <c r="E112" s="6"/>
+      <c r="B112" s="15"/>
+      <c r="C112" s="16"/>
+      <c r="D112" s="16"/>
+      <c r="E112" s="15"/>
       <c r="F112" s="6"/>
       <c r="G112" s="6"/>
       <c r="H112" s="8"/>
     </row>
     <row r="113" ht="22.5" customHeight="1">
       <c r="A113" s="6"/>
-      <c r="B113" s="17"/>
-      <c r="C113" s="18"/>
-      <c r="D113" s="18"/>
-      <c r="E113" s="6"/>
+      <c r="B113" s="15"/>
+      <c r="C113" s="16"/>
+      <c r="D113" s="16"/>
+      <c r="E113" s="15"/>
       <c r="F113" s="6"/>
       <c r="G113" s="6"/>
       <c r="H113" s="8"/>
     </row>
     <row r="114" ht="22.5" customHeight="1">
       <c r="A114" s="6"/>
-      <c r="B114" s="17"/>
-      <c r="C114" s="18"/>
-      <c r="D114" s="18"/>
-      <c r="E114" s="6"/>
+      <c r="B114" s="15"/>
+      <c r="C114" s="16"/>
+      <c r="D114" s="16"/>
+      <c r="E114" s="15"/>
       <c r="F114" s="6"/>
       <c r="G114" s="6"/>
       <c r="H114" s="8"/>
     </row>
     <row r="115" ht="22.5" customHeight="1">
       <c r="A115" s="6"/>
-      <c r="B115" s="17"/>
-      <c r="C115" s="18"/>
-      <c r="D115" s="18"/>
-      <c r="E115" s="6"/>
+      <c r="B115" s="15"/>
+      <c r="C115" s="16"/>
+      <c r="D115" s="16"/>
+      <c r="E115" s="15"/>
       <c r="F115" s="6"/>
       <c r="G115" s="6"/>
       <c r="H115" s="8"/>
     </row>
     <row r="116" ht="22.5" customHeight="1">
       <c r="A116" s="6"/>
-      <c r="B116" s="17"/>
-      <c r="C116" s="18"/>
-      <c r="D116" s="18"/>
-      <c r="E116" s="6"/>
+      <c r="B116" s="15"/>
+      <c r="C116" s="16"/>
+      <c r="D116" s="16"/>
+      <c r="E116" s="15"/>
       <c r="F116" s="6"/>
       <c r="G116" s="6"/>
       <c r="H116" s="8"/>
     </row>
     <row r="117" ht="22.5" customHeight="1">
       <c r="A117" s="6"/>
-      <c r="B117" s="17"/>
-      <c r="C117" s="18"/>
-      <c r="D117" s="18"/>
-      <c r="E117" s="6"/>
+      <c r="B117" s="15"/>
+      <c r="C117" s="16"/>
+      <c r="D117" s="16"/>
+      <c r="E117" s="15"/>
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
       <c r="H117" s="8"/>
     </row>
     <row r="118" ht="22.5" customHeight="1">
       <c r="A118" s="6"/>
-      <c r="B118" s="17"/>
-      <c r="C118" s="18"/>
-      <c r="D118" s="18"/>
-      <c r="E118" s="6"/>
+      <c r="B118" s="15"/>
+      <c r="C118" s="16"/>
+      <c r="D118" s="16"/>
+      <c r="E118" s="15"/>
       <c r="F118" s="6"/>
       <c r="G118" s="6"/>
       <c r="H118" s="8"/>
     </row>
     <row r="119" ht="22.5" customHeight="1">
       <c r="A119" s="6"/>
-      <c r="B119" s="17"/>
-      <c r="C119" s="18"/>
-      <c r="D119" s="18"/>
-      <c r="E119" s="6"/>
+      <c r="B119" s="15"/>
+      <c r="C119" s="16"/>
+      <c r="D119" s="16"/>
+      <c r="E119" s="15"/>
       <c r="F119" s="6"/>
       <c r="G119" s="6"/>
       <c r="H119" s="8"/>
     </row>
     <row r="120" ht="22.5" customHeight="1">
       <c r="A120" s="6"/>
-      <c r="B120" s="17"/>
-      <c r="C120" s="18"/>
-      <c r="D120" s="18"/>
-      <c r="E120" s="6"/>
+      <c r="B120" s="15"/>
+      <c r="C120" s="16"/>
+      <c r="D120" s="16"/>
+      <c r="E120" s="15"/>
       <c r="F120" s="6"/>
       <c r="G120" s="6"/>
       <c r="H120" s="8"/>
     </row>
     <row r="121" ht="22.5" customHeight="1">
       <c r="A121" s="6"/>
-      <c r="B121" s="17"/>
-      <c r="C121" s="18"/>
-      <c r="D121" s="18"/>
-      <c r="E121" s="6"/>
+      <c r="B121" s="15"/>
+      <c r="C121" s="16"/>
+      <c r="D121" s="16"/>
+      <c r="E121" s="15"/>
       <c r="F121" s="6"/>
       <c r="G121" s="6"/>
       <c r="H121" s="8"/>
     </row>
     <row r="122" ht="22.5" customHeight="1">
       <c r="A122" s="6"/>
-      <c r="B122" s="17"/>
-      <c r="C122" s="18"/>
-      <c r="D122" s="18"/>
-      <c r="E122" s="6"/>
+      <c r="B122" s="15"/>
+      <c r="C122" s="16"/>
+      <c r="D122" s="16"/>
+      <c r="E122" s="15"/>
       <c r="F122" s="6"/>
       <c r="G122" s="6"/>
       <c r="H122" s="8"/>
     </row>
     <row r="123" ht="22.5" customHeight="1">
       <c r="A123" s="6"/>
-      <c r="B123" s="17"/>
-      <c r="C123" s="18"/>
-      <c r="D123" s="18"/>
-      <c r="E123" s="6"/>
+      <c r="B123" s="15"/>
+      <c r="C123" s="16"/>
+      <c r="D123" s="16"/>
+      <c r="E123" s="15"/>
       <c r="F123" s="6"/>
       <c r="G123" s="6"/>
       <c r="H123" s="8"/>
     </row>
     <row r="124" ht="22.5" customHeight="1">
       <c r="A124" s="6"/>
-      <c r="B124" s="17"/>
-      <c r="C124" s="18"/>
-      <c r="D124" s="18"/>
-      <c r="E124" s="6"/>
+      <c r="B124" s="15"/>
+      <c r="C124" s="16"/>
+      <c r="D124" s="16"/>
+      <c r="E124" s="15"/>
       <c r="F124" s="6"/>
       <c r="G124" s="6"/>
       <c r="H124" s="8"/>
     </row>
     <row r="125" ht="22.5" customHeight="1">
       <c r="A125" s="6"/>
-      <c r="B125" s="17"/>
-      <c r="C125" s="18"/>
-      <c r="D125" s="18"/>
-      <c r="E125" s="6"/>
+      <c r="B125" s="15"/>
+      <c r="C125" s="16"/>
+      <c r="D125" s="16"/>
+      <c r="E125" s="15"/>
       <c r="F125" s="6"/>
       <c r="G125" s="6"/>
       <c r="H125" s="8"/>
     </row>
     <row r="126" ht="22.5" customHeight="1">
       <c r="A126" s="6"/>
-      <c r="B126" s="17"/>
-      <c r="C126" s="18"/>
-      <c r="D126" s="18"/>
-      <c r="E126" s="6"/>
+      <c r="B126" s="15"/>
+      <c r="C126" s="16"/>
+      <c r="D126" s="16"/>
+      <c r="E126" s="15"/>
       <c r="F126" s="6"/>
       <c r="G126" s="6"/>
       <c r="H126" s="8"/>
     </row>
     <row r="127" ht="22.5" customHeight="1">
       <c r="A127" s="6"/>
-      <c r="B127" s="17"/>
-      <c r="C127" s="18"/>
-      <c r="D127" s="18"/>
-      <c r="E127" s="6"/>
+      <c r="B127" s="15"/>
+      <c r="C127" s="16"/>
+      <c r="D127" s="16"/>
+      <c r="E127" s="15"/>
       <c r="F127" s="6"/>
       <c r="G127" s="6"/>
       <c r="H127" s="8"/>
     </row>
     <row r="128" ht="22.5" customHeight="1">
       <c r="A128" s="6"/>
-      <c r="B128" s="17"/>
-      <c r="C128" s="18"/>
-      <c r="D128" s="18"/>
-      <c r="E128" s="6"/>
+      <c r="B128" s="15"/>
+      <c r="C128" s="16"/>
+      <c r="D128" s="16"/>
+      <c r="E128" s="15"/>
       <c r="F128" s="6"/>
       <c r="G128" s="6"/>
       <c r="H128" s="8"/>
